--- a/scores.xlsx
+++ b/scores.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\rockpidinettrain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA89953D-CD93-4726-AA0D-0E806F7BEC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502F0E6B-C17C-4DF6-9868-0E5FAE2C8C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="1752" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F-score" sheetId="1" r:id="rId1"/>
+    <sheet name="ddn F-score" sheetId="4" r:id="rId2"/>
+    <sheet name="F-score-64" sheetId="3" r:id="rId3"/>
+    <sheet name="PQ" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
   <si>
     <t>PiDiNet: boundary F-score</t>
   </si>
@@ -77,23 +80,70 @@
     <t>PiDiNet: panoptic quality</t>
   </si>
   <si>
-    <t>0.099164793</t>
-  </si>
-  <si>
-    <t>0.011388580</t>
-  </si>
-  <si>
-    <t>0.062287207</t>
+    <t>th=64</t>
+  </si>
+  <si>
+    <t>stride = 128, size=512</t>
+  </si>
+  <si>
+    <t>stride = 512, crop= 1024</t>
+  </si>
+  <si>
+    <t>stride=392, size=512</t>
+  </si>
+  <si>
+    <t>1, lam=0</t>
+  </si>
+  <si>
+    <t>1, lam=5</t>
+  </si>
+  <si>
+    <t>2, lam=5</t>
+  </si>
+  <si>
+    <t>2, lam=0</t>
+  </si>
+  <si>
+    <t>0.407331272</t>
+  </si>
+  <si>
+    <t>0.517094720</t>
+  </si>
+  <si>
+    <t>0.620759754</t>
+  </si>
+  <si>
+    <t>0.339951643</t>
+  </si>
+  <si>
+    <t>0.500731744</t>
+  </si>
+  <si>
+    <t>0.344893136</t>
+  </si>
+  <si>
+    <t>0.499461871</t>
+  </si>
+  <si>
+    <t>0.545147906</t>
+  </si>
+  <si>
+    <t>0.362083740</t>
+  </si>
+  <si>
+    <t>0.401605489</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -148,8 +198,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,8 +238,20 @@
         <fgColor rgb="FFE9EEF5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -251,12 +320,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF334B6B"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF334B6B"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF334B6B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -267,21 +419,155 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -297,21 +583,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -526,26 +797,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="9" width="18" customWidth="1"/>
+    <col min="2" max="10" width="10.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.05" customHeight="1">
+    <row r="1" spans="1:15" ht="25.05" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="25.05" customHeight="1">
+    <row r="2" spans="1:15" ht="25.05" customHeight="1">
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="25.05" customHeight="1">
+    <row r="3" spans="1:15" ht="25.05" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -556,39 +827,46 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="25.05" customHeight="1">
+    <row r="4" spans="1:15" ht="25.05" customHeight="1">
       <c r="A4" s="5"/>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="21"/>
-    </row>
-    <row r="5" spans="1:9" ht="37.950000000000003" customHeight="1">
-      <c r="A5" s="7" t="s">
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:15" ht="37.950000000000003" customHeight="1">
+      <c r="A5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="14" t="s">
+      <c r="D5" s="61"/>
+      <c r="E5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
-    </row>
-    <row r="6" spans="1:9" ht="25.05" customHeight="1">
+      <c r="F5" s="30"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="32"/>
+      <c r="I5">
+        <v>192</v>
+      </c>
+      <c r="K5" s="33"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="17"/>
+    </row>
+    <row r="6" spans="1:15" ht="25.05" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
@@ -599,399 +877,779 @@
       <c r="D6" s="6">
         <v>2</v>
       </c>
-      <c r="E6" s="6">
-        <v>3</v>
-      </c>
-      <c r="F6" s="6">
-        <v>4</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="E6" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="H6" s="6">
-        <v>4</v>
-      </c>
-      <c r="I6" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="25.05" customHeight="1">
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+    </row>
+    <row r="7" spans="1:15" ht="25.05" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="15">
         <v>0.29960101248690674</v>
       </c>
-      <c r="C7" s="9">
-        <v>0.440050547966295</v>
-      </c>
-      <c r="D7" s="9">
-        <v>0.42800816831420835</v>
-      </c>
-      <c r="E7" s="9">
-        <v>0.43520229482248823</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0.4260150357305848</v>
-      </c>
-      <c r="G7" s="9">
-        <v>0.4022367673963248</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0.3895525285082615</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0.38564113546664702</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="25.05" customHeight="1">
+      <c r="C7" s="62">
+        <v>0.44368850999999998</v>
+      </c>
+      <c r="D7" s="62">
+        <v>0.434096133</v>
+      </c>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="64"/>
+      <c r="H7" s="19"/>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="18"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="18"/>
+    </row>
+    <row r="8" spans="1:15" ht="25.05" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="15">
         <v>0.48782025625752629</v>
       </c>
-      <c r="C8" s="9">
-        <v>0.51360713239824829</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0.51991881116219907</v>
-      </c>
-      <c r="E8" s="9">
-        <v>0.52217058165255636</v>
-      </c>
-      <c r="F8" s="8">
-        <v>0.51938961532015981</v>
-      </c>
-      <c r="G8" s="9">
-        <v>0.51126672066815748</v>
-      </c>
-      <c r="H8" s="8">
-        <v>0.51510113123135504</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0.5142675554415419</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="25.05" customHeight="1">
+      <c r="C8" s="62">
+        <v>0.51994613000000001</v>
+      </c>
+      <c r="D8" s="62">
+        <v>0.51815958399999995</v>
+      </c>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="64"/>
+      <c r="H8" s="19"/>
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="18"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="18"/>
+    </row>
+    <row r="9" spans="1:15" ht="25.05" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="15">
         <v>0.52295169087459048</v>
       </c>
-      <c r="C9" s="9">
-        <v>0.6418624714578125</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0.63767722499275059</v>
-      </c>
-      <c r="E9" s="9">
-        <v>0.63942517638810603</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0.62933099192598241</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0.60488552087902503</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0.60216944992359966</v>
-      </c>
-      <c r="I9" s="9">
-        <v>0.59705835573538768</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="25.05" customHeight="1">
+      <c r="C9" s="62">
+        <v>0.64849654999999995</v>
+      </c>
+      <c r="D9" s="62">
+        <v>0.642898423</v>
+      </c>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="64"/>
+      <c r="H9" s="19"/>
+      <c r="I9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="18"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" spans="1:15" ht="25.05" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="15">
         <v>0.36544650811281948</v>
       </c>
-      <c r="C10" s="9">
-        <v>0.30335457029720625</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0.31832367794635591</v>
-      </c>
-      <c r="E10" s="9">
-        <v>0.3047488778522725</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.31581794831892923</v>
-      </c>
-      <c r="G10" s="9">
-        <v>0.34488937284022403</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0.34411828509317371</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0.34693353139658323</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="25.05" customHeight="1">
+      <c r="C10" s="62">
+        <v>0.30531786799999999</v>
+      </c>
+      <c r="D10" s="62">
+        <v>0.31880282199999999</v>
+      </c>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="64"/>
+      <c r="H10" s="19"/>
+      <c r="I10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="18"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="18"/>
+    </row>
+    <row r="11" spans="1:15" ht="25.05" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="15">
         <v>0.38352293822875039</v>
       </c>
-      <c r="C11" s="9">
-        <v>0.55827759562725443</v>
-      </c>
-      <c r="D11" s="9">
-        <v>0.53697189128041256</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.55249467509894767</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0.53601411806677157</v>
-      </c>
-      <c r="G11" s="9">
-        <v>0.48244342632610698</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0.48559056312450388</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0.47814101893594096</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="25.05" customHeight="1">
-      <c r="A12" s="10" t="s">
+      <c r="C11" s="62">
+        <v>0.49467475300000002</v>
+      </c>
+      <c r="D11" s="62">
+        <v>0.54570070500000001</v>
+      </c>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="19"/>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="18"/>
+    </row>
+    <row r="12" spans="1:15" ht="25.05" customHeight="1">
+      <c r="A12" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="11">
-        <f>AVERAGE(B7:B11)</f>
+      <c r="B12" s="16">
+        <f t="shared" ref="B12" si="0">AVERAGE(B7:B11)</f>
         <v>0.41186848119211861</v>
       </c>
-      <c r="C12" s="12">
-        <f t="shared" ref="C12:I12" si="0">AVERAGE(C7:C11)</f>
-        <v>0.49143046354936332</v>
-      </c>
-      <c r="D12" s="12">
-        <f t="shared" si="0"/>
-        <v>0.4881799547391853</v>
-      </c>
-      <c r="E12" s="12">
-        <f t="shared" si="0"/>
-        <v>0.49080832116287415</v>
-      </c>
-      <c r="F12" s="11">
-        <f t="shared" si="0"/>
-        <v>0.48531354187248554</v>
-      </c>
-      <c r="G12" s="12">
-        <f t="shared" si="0"/>
-        <v>0.46914436162196765</v>
-      </c>
-      <c r="H12" s="11">
-        <f t="shared" si="0"/>
-        <v>0.4673063915761787</v>
-      </c>
-      <c r="I12" s="13">
-        <f t="shared" si="0"/>
-        <v>0.4644083193952202</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="25.05" customHeight="1"/>
-    <row r="14" spans="1:9" ht="25.05" customHeight="1"/>
-    <row r="15" spans="1:9" ht="25.05" customHeight="1"/>
-    <row r="16" spans="1:9" ht="25.05" customHeight="1"/>
-    <row r="17" spans="1:9" ht="21">
-      <c r="A17" s="5"/>
-      <c r="B17" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="21"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="18"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6">
-        <v>1</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2</v>
-      </c>
-      <c r="E19" s="6">
-        <v>3</v>
-      </c>
-      <c r="F19" s="6">
-        <v>4</v>
-      </c>
-      <c r="G19" s="6">
-        <v>1</v>
-      </c>
-      <c r="H19" s="6">
-        <v>4</v>
-      </c>
-      <c r="I19" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9">
-        <v>2.257754E-2</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8">
-        <v>1.9694672999999999E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="9">
-        <v>2.6907562999999999E-2</v>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8">
-        <v>3.1896283999999997E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="23">
-        <v>8.6711712999999996E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8">
-        <v>1.2759491E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="23">
-        <v>4.0309307000000003E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="11" t="e">
-        <f>AVERAGE(B20:B24)</f>
+      <c r="C12" s="65">
+        <f>AVERAGE(C7:C11)</f>
+        <v>0.48242476219999997</v>
+      </c>
+      <c r="D12" s="66">
+        <f>AVERAGE(D7:D11)</f>
+        <v>0.49193153340000001</v>
+      </c>
+      <c r="E12" s="66"/>
+      <c r="F12" s="65" t="e">
+        <f>AVERAGE(F7:F11)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C25" s="12">
-        <f>AVERAGE(C20:C24)</f>
-        <v>2.4742551500000001E-2</v>
-      </c>
-      <c r="D25" s="12" t="e">
-        <f t="shared" ref="D25" si="1">AVERAGE(D20:D24)</f>
+      <c r="G12" s="66" t="e">
+        <f>AVERAGE(G7:G11)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E25" s="12" t="e">
-        <f t="shared" ref="E25" si="2">AVERAGE(E20:E24)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F25" s="11" t="e">
-        <f t="shared" ref="F25" si="3">AVERAGE(F20:F24)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G25" s="12" t="e">
-        <f t="shared" ref="G25" si="4">AVERAGE(G20:G24)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H25" s="11" t="e">
-        <f t="shared" ref="H25" si="5">AVERAGE(H20:H24)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I25" s="13">
-        <f>AVERAGE(I20:I24)</f>
-        <v>3.8274293599999995E-2</v>
-      </c>
-    </row>
+      <c r="H12" s="21">
+        <v>0.49968299799999999</v>
+      </c>
+      <c r="K12" s="20"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="22"/>
+      <c r="O12" s="22"/>
+    </row>
+    <row r="13" spans="1:15" ht="25.05" customHeight="1"/>
+    <row r="14" spans="1:15" ht="25.05" customHeight="1"/>
+    <row r="15" spans="1:15" ht="25.05" customHeight="1"/>
+    <row r="16" spans="1:15" ht="25.05" customHeight="1"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:I18"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40172B9-2564-4685-BE52-FD0A30AE3D13}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="21">
+      <c r="A1" s="5"/>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="12"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="32"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15">
+        <v>0.33862549800000002</v>
+      </c>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="19"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16">
+        <f t="shared" ref="B9" si="0">AVERAGE(B4:B8)</f>
+        <v>0.33862549800000002</v>
+      </c>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E4173D-FFFB-4613-8853-3B75CBD16295}">
+  <dimension ref="B5:K13"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="2" max="2" width="14.69921875" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" customWidth="1"/>
+    <col min="5" max="5" width="11.09765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:11">
+      <c r="B5" s="5"/>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="58"/>
+      <c r="F6" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="41"/>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="55">
+        <v>1</v>
+      </c>
+      <c r="E7" s="55">
+        <v>2</v>
+      </c>
+      <c r="F7" s="52">
+        <v>1</v>
+      </c>
+      <c r="G7" s="42">
+        <v>2</v>
+      </c>
+      <c r="H7" s="42">
+        <v>3</v>
+      </c>
+      <c r="I7" s="42">
+        <v>4</v>
+      </c>
+      <c r="J7" s="59">
+        <v>1</v>
+      </c>
+      <c r="K7" s="59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="50">
+        <v>0.29960101248690674</v>
+      </c>
+      <c r="D8" s="56">
+        <v>0.215675798</v>
+      </c>
+      <c r="E8" s="56"/>
+      <c r="F8" s="53">
+        <v>0.440050547966295</v>
+      </c>
+      <c r="G8" s="46">
+        <v>0.42800816831420835</v>
+      </c>
+      <c r="H8" s="46">
+        <v>0.43520229482248823</v>
+      </c>
+      <c r="I8" s="44">
+        <v>0.4260150357305848</v>
+      </c>
+      <c r="J8" s="45">
+        <v>0.44368850999999998</v>
+      </c>
+      <c r="K8" s="45">
+        <v>0.434096133</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="50">
+        <v>0.48782025625752629</v>
+      </c>
+      <c r="D9" s="56">
+        <v>0.324070731</v>
+      </c>
+      <c r="E9" s="56"/>
+      <c r="F9" s="53">
+        <v>0.51360713239824829</v>
+      </c>
+      <c r="G9" s="46">
+        <v>0.51991881116219907</v>
+      </c>
+      <c r="H9" s="46">
+        <v>0.52217058165255636</v>
+      </c>
+      <c r="I9" s="44">
+        <v>0.51938961532015981</v>
+      </c>
+      <c r="J9" s="45">
+        <v>0.51994613000000001</v>
+      </c>
+      <c r="K9" s="45">
+        <v>0.51815958399999995</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="50">
+        <v>0.52295169087459048</v>
+      </c>
+      <c r="D10" s="56">
+        <v>0.397705788</v>
+      </c>
+      <c r="E10" s="56"/>
+      <c r="F10" s="53">
+        <v>0.6418624714578125</v>
+      </c>
+      <c r="G10" s="46">
+        <v>0.63767722499275059</v>
+      </c>
+      <c r="H10" s="46">
+        <v>0.63942517638810603</v>
+      </c>
+      <c r="I10" s="44">
+        <v>0.62933099192598241</v>
+      </c>
+      <c r="J10" s="45">
+        <v>0.64849654999999995</v>
+      </c>
+      <c r="K10" s="45">
+        <v>0.642898423</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="50">
+        <v>0.36544650811281948</v>
+      </c>
+      <c r="D11" s="56">
+        <v>0.184432129</v>
+      </c>
+      <c r="E11" s="56"/>
+      <c r="F11" s="53">
+        <v>0.30335457029720625</v>
+      </c>
+      <c r="G11" s="46">
+        <v>0.31832367794635591</v>
+      </c>
+      <c r="H11" s="46">
+        <v>0.3047488778522725</v>
+      </c>
+      <c r="I11" s="44">
+        <v>0.31581794831892923</v>
+      </c>
+      <c r="J11" s="45">
+        <v>0.30531786799999999</v>
+      </c>
+      <c r="K11" s="45">
+        <v>0.31880282199999999</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="50">
+        <v>0.38352293822875039</v>
+      </c>
+      <c r="D12" s="56">
+        <v>0.33107777900000002</v>
+      </c>
+      <c r="E12" s="56"/>
+      <c r="F12" s="53">
+        <v>0.55827759562725443</v>
+      </c>
+      <c r="G12" s="46">
+        <v>0.53697189128041256</v>
+      </c>
+      <c r="H12" s="46">
+        <v>0.55249467509894767</v>
+      </c>
+      <c r="I12" s="44">
+        <v>0.53601411806677157</v>
+      </c>
+      <c r="J12" s="45">
+        <v>0.49467475300000002</v>
+      </c>
+      <c r="K12" s="45">
+        <v>0.54570070500000001</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="30" customHeight="1">
+      <c r="B13" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="51">
+        <f t="shared" ref="C13:D13" si="0">AVERAGE(C8:C12)</f>
+        <v>0.41186848119211861</v>
+      </c>
+      <c r="D13" s="57">
+        <f t="shared" si="0"/>
+        <v>0.29059244499999998</v>
+      </c>
+      <c r="E13" s="56"/>
+      <c r="F13" s="54">
+        <f t="shared" ref="F13:K13" si="1">AVERAGE(F8:F12)</f>
+        <v>0.49143046354936332</v>
+      </c>
+      <c r="G13" s="48">
+        <f t="shared" si="1"/>
+        <v>0.4881799547391853</v>
+      </c>
+      <c r="H13" s="48">
+        <f t="shared" si="1"/>
+        <v>0.49080832116287415</v>
+      </c>
+      <c r="I13" s="47">
+        <f t="shared" si="1"/>
+        <v>0.48531354187248554</v>
+      </c>
+      <c r="J13" s="47">
+        <f t="shared" si="1"/>
+        <v>0.48242476219999997</v>
+      </c>
+      <c r="K13" s="47">
+        <f t="shared" si="1"/>
+        <v>0.49193153340000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20ECF1A6-17CB-4F5E-8A81-EEB9AEA80637}">
+  <dimension ref="B3:J11"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetData>
+    <row r="3" spans="2:10" ht="21">
+      <c r="B3" s="5"/>
+      <c r="C3" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="69"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="73"/>
+      <c r="J4" s="74"/>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
+        <v>2</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6">
+        <v>4</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6">
+        <v>4</v>
+      </c>
+      <c r="J5" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="25">
+        <v>2.257754E-2</v>
+      </c>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24">
+        <v>1.9694672999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25">
+        <v>2.6907562999999999E-2</v>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24">
+        <v>3.1896283999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="25">
+        <v>9.9164793000000001E-2</v>
+      </c>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="26">
+        <v>8.6711712999999996E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25">
+        <v>1.1388580000000001E-2</v>
+      </c>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24">
+        <v>1.2759491E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="26"/>
+      <c r="D10" s="25">
+        <v>6.2287206999999997E-2</v>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="26">
+        <v>4.0309307000000003E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="27" t="e">
+        <f t="shared" ref="C11:J11" si="0">AVERAGE(C6:C10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D11" s="28">
+        <f t="shared" si="0"/>
+        <v>4.4465136599999996E-2</v>
+      </c>
+      <c r="E11" s="28" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F11" s="28" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G11" s="27" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H11" s="28" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I11" s="27" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J11" s="29">
+        <f t="shared" si="0"/>
+        <v>3.8274293599999995E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="H4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>